--- a/subir/fixture.xlsx
+++ b/subir/fixture.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\appflutter\handball_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\appflutter\handball_app\subir\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
   <si>
     <t>Fecha</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>A.A.C.F. Quilmes</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Cadetes</t>
+  </si>
+  <si>
+    <t>Torneo</t>
+  </si>
+  <si>
+    <t>Apertura</t>
   </si>
 </sst>
 </file>
@@ -122,9 +134,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,30 +420,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -441,8 +463,14 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -455,8 +483,14 @@
       <c r="D3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -469,8 +503,14 @@
       <c r="D4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -483,8 +523,14 @@
       <c r="D5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -497,8 +543,14 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -511,8 +563,14 @@
       <c r="D7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -525,8 +583,14 @@
       <c r="D8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -539,8 +603,14 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -553,8 +623,14 @@
       <c r="D10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -567,8 +643,14 @@
       <c r="D11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -581,8 +663,14 @@
       <c r="D12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -595,8 +683,14 @@
       <c r="D13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -609,8 +703,14 @@
       <c r="D14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -623,8 +723,14 @@
       <c r="D15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -636,6 +742,12 @@
       </c>
       <c r="D16" t="s">
         <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
